--- a/datasets/rbf_validacao.xlsx
+++ b/datasets/rbf_validacao.xlsx
@@ -494,31 +494,31 @@
         <v>-1</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.00240604</v>
+        <v>-1.00239457</v>
       </c>
       <c r="E2" t="n">
         <v>-1</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.00240167</v>
+        <v>-1.00237238</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0023978</v>
+        <v>-1.00238906</v>
       </c>
       <c r="I2" t="n">
         <v>-1</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.00242042</v>
+        <v>-1.00237468</v>
       </c>
       <c r="K2" t="n">
         <v>-1</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.00239684</v>
+        <v>-1.00240043</v>
       </c>
       <c r="M2" t="n">
         <v>-1</v>
@@ -535,31 +535,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.32309383</v>
+        <v>-0.3230905</v>
       </c>
       <c r="E3" t="n">
         <v>-1</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.32309256</v>
+        <v>-0.32308405</v>
       </c>
       <c r="G3" t="n">
         <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.32309143</v>
+        <v>-0.3230889</v>
       </c>
       <c r="I3" t="n">
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.32309801</v>
+        <v>-0.32308472</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.32309116</v>
+        <v>-0.3230922</v>
       </c>
       <c r="M3" t="n">
         <v>-1</v>
@@ -576,31 +576,31 @@
         <v>-1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.91394979</v>
+        <v>-0.91393897</v>
       </c>
       <c r="E4" t="n">
         <v>-1</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.91394566</v>
+        <v>-0.91391805</v>
       </c>
       <c r="G4" t="n">
         <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.91394201</v>
+        <v>-0.91393378</v>
       </c>
       <c r="I4" t="n">
         <v>-1</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.91396334</v>
+        <v>-0.9139202199999999</v>
       </c>
       <c r="K4" t="n">
         <v>-1</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.91394111</v>
+        <v>-0.91394449</v>
       </c>
       <c r="M4" t="n">
         <v>-1</v>
@@ -617,31 +617,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.22002622</v>
+        <v>-0.22002044</v>
       </c>
       <c r="E5" t="n">
         <v>-1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.22002402</v>
+        <v>-0.22000925</v>
       </c>
       <c r="G5" t="n">
         <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.22002208</v>
+        <v>-0.22001766</v>
       </c>
       <c r="I5" t="n">
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.22003348</v>
+        <v>-0.22001041</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.22002159</v>
+        <v>-0.2200234</v>
       </c>
       <c r="M5" t="n">
         <v>-1</v>
@@ -658,31 +658,31 @@
         <v>-1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.00247859</v>
+        <v>-1.00246712</v>
       </c>
       <c r="E6" t="n">
         <v>-1</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.00247422</v>
+        <v>-1.00244492</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.00247034</v>
+        <v>-1.00246161</v>
       </c>
       <c r="I6" t="n">
         <v>-1</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.00249296</v>
+        <v>-1.00244723</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.00246938</v>
+        <v>-1.00247297</v>
       </c>
       <c r="M6" t="n">
         <v>-1</v>
@@ -699,31 +699,31 @@
         <v>-1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9876856899999999</v>
+        <v>-0.9876745</v>
       </c>
       <c r="E7" t="n">
         <v>-1</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.98768142</v>
+        <v>-0.98765286</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.98767764</v>
+        <v>-0.98766913</v>
       </c>
       <c r="I7" t="n">
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.98769971</v>
+        <v>-0.9876551099999999</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.98767671</v>
+        <v>-0.9876802099999999</v>
       </c>
       <c r="M7" t="n">
         <v>-1</v>
@@ -740,31 +740,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.96643353</v>
+        <v>0.9664248600000001</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.96643022</v>
+        <v>0.96640806</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.96642729</v>
+        <v>0.96642069</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9664444</v>
+        <v>0.96640981</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.96642657</v>
+        <v>0.9664292799999999</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -781,31 +781,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.32312504</v>
+        <v>1.32311674</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.32312187</v>
+        <v>1.32310064</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.32311904</v>
+        <v>1.32311274</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.32313544</v>
+        <v>1.32310232</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32311836</v>
+        <v>1.32312096</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -822,31 +822,31 @@
         <v>-1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.46812829</v>
+        <v>-0.46812137</v>
       </c>
       <c r="E10" t="n">
         <v>-1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.46812565</v>
+        <v>-0.46810797</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.46812332</v>
+        <v>-0.46811804</v>
       </c>
       <c r="I10" t="n">
         <v>-1</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.46813698</v>
+        <v>-0.46810936</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.46812274</v>
+        <v>-0.4681249</v>
       </c>
       <c r="M10" t="n">
         <v>-1</v>
@@ -863,31 +863,31 @@
         <v>-1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.99655761</v>
+        <v>-0.9965461799999999</v>
       </c>
       <c r="E11" t="n">
         <v>-1</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9965532499999999</v>
+        <v>-0.99652407</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.99654939</v>
+        <v>-0.99654069</v>
       </c>
       <c r="I11" t="n">
         <v>-1</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.99657193</v>
+        <v>-0.99652637</v>
       </c>
       <c r="K11" t="n">
         <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.99654844</v>
+        <v>-0.99655202</v>
       </c>
       <c r="M11" t="n">
         <v>-1</v>

--- a/datasets/rbf_validacao.xlsx
+++ b/datasets/rbf_validacao.xlsx
@@ -494,31 +494,31 @@
         <v>-1</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.00239457</v>
+        <v>-1.27331842</v>
       </c>
       <c r="E2" t="n">
         <v>-1</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.00237238</v>
+        <v>-1.27337584</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.00238906</v>
+        <v>-1.27335554</v>
       </c>
       <c r="I2" t="n">
         <v>-1</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.00237468</v>
+        <v>-1.27338234</v>
       </c>
       <c r="K2" t="n">
         <v>-1</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.00240043</v>
+        <v>-1.27331084</v>
       </c>
       <c r="M2" t="n">
         <v>-1</v>
@@ -535,34 +535,34 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3230905</v>
+        <v>0.22086064</v>
       </c>
       <c r="E3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.32308405</v>
+        <v>0.22087159</v>
       </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3230889</v>
+        <v>0.22086777</v>
       </c>
       <c r="I3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.32308472</v>
+        <v>0.22087281</v>
       </c>
       <c r="K3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3230922</v>
+        <v>0.22085913</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -576,31 +576,31 @@
         <v>-1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.91393897</v>
+        <v>-0.81101667</v>
       </c>
       <c r="E4" t="n">
         <v>-1</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.91391805</v>
+        <v>-0.81106017</v>
       </c>
       <c r="G4" t="n">
         <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.91393378</v>
+        <v>-0.81104487</v>
       </c>
       <c r="I4" t="n">
         <v>-1</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9139202199999999</v>
+        <v>-0.81106506</v>
       </c>
       <c r="K4" t="n">
         <v>-1</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.91394449</v>
+        <v>-0.81101081</v>
       </c>
       <c r="M4" t="n">
         <v>-1</v>
@@ -617,34 +617,34 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.22002044</v>
+        <v>0.07533424</v>
       </c>
       <c r="E5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.22000925</v>
+        <v>0.07531454</v>
       </c>
       <c r="G5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.22001766</v>
+        <v>0.07532121</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.22001041</v>
+        <v>0.07531239000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2200234</v>
+        <v>0.07533721</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -658,31 +658,31 @@
         <v>-1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.00246712</v>
+        <v>-1.27833482</v>
       </c>
       <c r="E6" t="n">
         <v>-1</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.00244492</v>
+        <v>-1.27839267</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.00246161</v>
+        <v>-1.27837222</v>
       </c>
       <c r="I6" t="n">
         <v>-1</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.00244723</v>
+        <v>-1.27839922</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.00247297</v>
+        <v>-1.27832717</v>
       </c>
       <c r="M6" t="n">
         <v>-1</v>
@@ -699,31 +699,31 @@
         <v>-1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9876745</v>
+        <v>-1.1354469</v>
       </c>
       <c r="E7" t="n">
         <v>-1</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.98765286</v>
+        <v>-1.1354945</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.98766913</v>
+        <v>-1.13547762</v>
       </c>
       <c r="I7" t="n">
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9876551099999999</v>
+        <v>-1.13549991</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9876802099999999</v>
+        <v>-1.13544068</v>
       </c>
       <c r="M7" t="n">
         <v>-1</v>
@@ -740,31 +740,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9664248600000001</v>
+        <v>1.28133261</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.96640806</v>
+        <v>1.28138249</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.96642069</v>
+        <v>1.28136481</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.96640981</v>
+        <v>1.28138815</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9664292799999999</v>
+        <v>1.28132607</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -781,31 +781,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.32311674</v>
+        <v>1.40945644</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.32310064</v>
+        <v>1.40949867</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.32311274</v>
+        <v>1.40948351</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.32310232</v>
+        <v>1.40950352</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32312096</v>
+        <v>1.40945115</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -822,34 +822,34 @@
         <v>-1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.46812137</v>
+        <v>0.00119784</v>
       </c>
       <c r="E10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.46810797</v>
+        <v>0.00118758</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.46811804</v>
+        <v>0.0011911</v>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.46810936</v>
+        <v>0.00118646</v>
       </c>
       <c r="K10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4681249</v>
+        <v>0.00119933</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -863,31 +863,31 @@
         <v>-1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9965461799999999</v>
+        <v>-1.17305652</v>
       </c>
       <c r="E11" t="n">
         <v>-1</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.99652407</v>
+        <v>-1.17311149</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.99654069</v>
+        <v>-1.17309208</v>
       </c>
       <c r="I11" t="n">
         <v>-1</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.99652637</v>
+        <v>-1.17311771</v>
       </c>
       <c r="K11" t="n">
         <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.99655202</v>
+        <v>-1.17304922</v>
       </c>
       <c r="M11" t="n">
         <v>-1</v>
